--- a/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/08_BIBS_UXScreens_BRD-05_Accounting_Disbursement_ACSL_v2.1.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/08_BIBS_UXScreens_BRD-05_Accounting_Disbursement_ACSL_v2.1.xlsx
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K146" s="45" t="inlineStr">
         <is>
-          <t>Insurer SOA reconciliation report: first page as generated</t>
+          <t>Insurer SOA reconciliation report: first page as generated, with the report header and the reconciliation columns (the remittance, 2307 and cancellation columns of the workbook are left out of the image)</t>
         </is>
       </c>
       <c r="L146" s="45" t="inlineStr">
